--- a/output/pdf_financials_xlsx/INO.UN.xlsx
+++ b/output/pdf_financials_xlsx/INO.UN.xlsx
@@ -1851,28 +1851,28 @@
         <v>6.895</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>9.657</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.345</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>6.201</v>
+        <v>76.627</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>9.474</v>
+        <v>0.176</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.045</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.249</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.006</v>
       </c>
     </row>
     <row r="35">
@@ -1925,28 +1925,28 @@
         <v>6.895</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>9.657</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.345</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>6.201</v>
+        <v>76.627</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>9.474</v>
+        <v>0.176</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.045</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.249</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.006</v>
       </c>
     </row>
     <row r="37">
@@ -6320,7 +6320,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -8640,7 +8640,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -10918,7 +10918,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -18468,7 +18468,7 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
@@ -21484,7 +21484,7 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">

--- a/output/pdf_financials_xlsx/INO.UN.xlsx
+++ b/output/pdf_financials_xlsx/INO.UN.xlsx
@@ -3209,22 +3209,22 @@
         <v>0</v>
       </c>
       <c r="F70" s="3" t="n">
-        <v>0</v>
+        <v>0.637</v>
       </c>
       <c r="G70" s="3" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="H70" s="3" t="n">
-        <v>0</v>
+        <v>0.424</v>
       </c>
       <c r="I70" s="3" t="n">
-        <v>0</v>
+        <v>0.006</v>
       </c>
       <c r="J70" s="3" t="n">
-        <v>0</v>
+        <v>0.035</v>
       </c>
       <c r="K70" s="3" t="n">
-        <v>0</v>
+        <v>0.005</v>
       </c>
     </row>
     <row r="71">
@@ -3246,22 +3246,22 @@
         <v>0</v>
       </c>
       <c r="F71" s="3" t="n">
-        <v>0</v>
+        <v>0.637</v>
       </c>
       <c r="G71" s="3" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="H71" s="3" t="n">
-        <v>0</v>
+        <v>0.424</v>
       </c>
       <c r="I71" s="3" t="n">
-        <v>0</v>
+        <v>0.006</v>
       </c>
       <c r="J71" s="3" t="n">
-        <v>0</v>
+        <v>0.035</v>
       </c>
       <c r="K71" s="3" t="n">
-        <v>0</v>
+        <v>0.005</v>
       </c>
     </row>
     <row r="72">
@@ -3394,7 +3394,7 @@
         <v>0.431</v>
       </c>
       <c r="F75" s="3" t="n">
-        <v>0.372</v>
+        <v>0</v>
       </c>
       <c r="G75" s="3" t="n">
         <v>5.327</v>
@@ -3403,13 +3403,13 @@
         <v>7.298</v>
       </c>
       <c r="I75" s="3" t="n">
-        <v>0.052</v>
+        <v>0.046</v>
       </c>
       <c r="J75" s="3" t="n">
-        <v>0.313</v>
+        <v>0.278</v>
       </c>
       <c r="K75" s="3" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.064</v>
       </c>
     </row>
     <row r="76">
@@ -3587,22 +3587,22 @@
         </is>
       </c>
       <c r="F80" s="3" t="n">
-        <v>2.269709543568465</v>
+        <v>4.912863070539419</v>
       </c>
       <c r="G80" s="3" t="n">
-        <v>0.3072973402487828</v>
+        <v>0.3295462097461606</v>
       </c>
       <c r="H80" s="3" t="n">
-        <v>0.6836158192090396</v>
+        <v>3.07909604519774</v>
       </c>
       <c r="I80" s="3" t="n">
-        <v>0.3541666666666667</v>
+        <v>0.375</v>
       </c>
       <c r="J80" s="3" t="n">
-        <v>7.161904761904762</v>
+        <v>7.495238095238095</v>
       </c>
       <c r="K80" s="3" t="n">
-        <v>0.521978021978022</v>
+        <v>0.5494505494505495</v>
       </c>
     </row>
     <row r="81">
@@ -7046,7 +7046,11 @@
           <t>Lease liabilities 13 12 999</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr">
         <is>
           <t>-</t>
@@ -9436,7 +9440,11 @@
           <t>Lease liabilities 13 6 819</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr"/>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E58" t="inlineStr">
         <is>
           <t>-</t>
@@ -11474,7 +11482,11 @@
           <t>Lease liabilities 13</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr"/>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E90" t="inlineStr">
         <is>
           <t>-</t>
@@ -19698,7 +19710,11 @@
           <t>Lease liabilities 16 6 910 6</t>
         </is>
       </c>
-      <c r="D215" t="inlineStr"/>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E215" t="inlineStr">
         <is>
           <t>-</t>
@@ -45648,7 +45664,11 @@
           <t>Deferred income tax recovery 22 557</t>
         </is>
       </c>
-      <c r="D614" t="inlineStr"/>
+      <c r="D614" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E614" t="inlineStr">
         <is>
           <t>-</t>
@@ -45712,7 +45732,11 @@
           <t>Total income tax recovery 328</t>
         </is>
       </c>
-      <c r="D615" t="inlineStr"/>
+      <c r="D615" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E615" t="inlineStr">
         <is>
           <t>-</t>
@@ -47022,7 +47046,11 @@
           <t>Deferred income tax recovery 21</t>
         </is>
       </c>
-      <c r="D635" t="inlineStr"/>
+      <c r="D635" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E635" t="inlineStr">
         <is>
           <t>-</t>
@@ -47086,7 +47114,11 @@
           <t>Total income tax recovery (expense)</t>
         </is>
       </c>
-      <c r="D636" t="inlineStr"/>
+      <c r="D636" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E636" t="inlineStr">
         <is>
           <t>-</t>
